--- a/mockups/cf_sample_output.xlsx
+++ b/mockups/cf_sample_output.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="152">
   <si>
     <t>サンプルサイト株式会社 分析レポート</t>
   </si>
@@ -49,7 +49,7 @@
     <t>生成日時</t>
   </si>
   <si>
-    <t>2026/04/17 11:59</t>
+    <t>2026/04/21 12:20</t>
   </si>
   <si>
     <t xml:space="preserve">  主要サマリー</t>
@@ -256,12 +256,6 @@
     <t>purchase</t>
   </si>
   <si>
-    <t>■ AI分析</t>
-  </si>
-  <si>
-    <t>対象期間中、セッション数は前年同月比で +15.5% と健全に成長しています。一方でモバイルのエンゲージメント率がやや低下しており、改善余地があります。</t>
-  </si>
-  <si>
     <t>月</t>
   </si>
   <si>
@@ -328,9 +322,6 @@
     <t>合計 / 平均</t>
   </si>
   <si>
-    <t>直近 3 ヶ月で CV 数が顕著に伸びています。2026 年 4 月は前月比 +5.8%。</t>
-  </si>
-  <si>
     <t>チャネル</t>
   </si>
   <si>
@@ -436,12 +427,12 @@
     <t>タイトル</t>
   </si>
   <si>
+    <t>対象URL</t>
+  </si>
+  <si>
     <t>説明</t>
   </si>
   <si>
-    <t>対象URL</t>
-  </si>
-  <si>
     <t>期待効果</t>
   </si>
   <si>
@@ -457,12 +448,12 @@
     <t>LP のヒーロー画像を最適化</t>
   </si>
   <si>
+    <t>/lp/main</t>
+  </si>
+  <si>
     <t>ファーストビューの離脱率改善のため、画像を WebP 化し圧縮。</t>
   </si>
   <si>
-    <t>/lp/main</t>
-  </si>
-  <si>
     <t>離脱率 -10%</t>
   </si>
   <si>
@@ -478,10 +469,10 @@
     <t>問い合わせフォーム項目削減</t>
   </si>
   <si>
+    <t>/contact</t>
+  </si>
+  <si>
     <t>10 項目 → 5 項目に削減し送信完了率を向上。</t>
-  </si>
-  <si>
-    <t>/contact</t>
   </si>
   <si>
     <t>送信完了率 +15%</t>
@@ -495,7 +486,7 @@
     <numFmt numFmtId="164" formatCode="#,##0"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,15 +595,8 @@
       <name val="Yu Gothic"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -643,20 +627,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7C3AED"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F3FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -770,36 +742,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7C3AED"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7C3AED"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7C3AED"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7C3AED"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDDD6FE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDDD6FE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDDD6FE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDDD6FE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF2347A0"/>
       </left>
       <right style="thin">
@@ -817,7 +759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -896,19 +838,13 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1005,7 +941,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>全体サマリー!$B$25:$B$26</c:f>
+              <c:f>全体サマリー!$D$25:$D$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -2010,8 +1946,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2030,6 +1966,132 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="7648575"/>
+          <a:ext cx="6591300" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F5F3FF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="DDD6FE"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="7C3AED"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>  ■ AI分析</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="1857375"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="7953375"/>
+          <a:ext cx="6591300" cy="1857375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F5F3FF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="DDD6FE"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" i="0">
+              <a:solidFill>
+                <a:srgbClr val="1E293B"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>対象期間中、セッション数は前年同月比で +15.5% と健全に成長しています。一方でモバイルのエンゲージメント率がやや低下しており、改善余地があります。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2065,6 +2127,132 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="5972175"/>
+          <a:ext cx="6591300" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F5F3FF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="DDD6FE"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="7C3AED"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>  ■ AI分析</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="1857375"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="6276975"/>
+          <a:ext cx="6591300" cy="1857375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F5F3FF"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="DDD6FE"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" i="0">
+              <a:solidFill>
+                <a:srgbClr val="1E293B"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>直近 3 ヶ月で CV 数が顕著に伸びています。2026 年 4 月は前月比 +5.8%。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2080,8 +2268,8 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2100,6 +2288,394 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="7000875"/>
+          <a:ext cx="6591300" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F9FAFB"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="E5E7EB"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="7C3AED"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>  ■ AI分析</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="1857375"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="7305675"/>
+          <a:ext cx="6591300" cy="1857375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F9FAFB"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="E5E7EB"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" i="1">
+              <a:solidFill>
+                <a:srgbClr val="9CA3AF"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>※ 画面で AI 分析を生成するとここに表示されます</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="3838575"/>
+          <a:ext cx="6591300" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F9FAFB"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="E5E7EB"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="7C3AED"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>  ■ AI分析</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="1857375"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="4143375"/>
+          <a:ext cx="6591300" cy="1857375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F9FAFB"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="E5E7EB"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" i="1">
+              <a:solidFill>
+                <a:srgbClr val="9CA3AF"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>※ 画面で AI 分析を生成するとここに表示されます</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="304800"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="2809875"/>
+          <a:ext cx="6591300" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F9FAFB"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="E5E7EB"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="7C3AED"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>  ■ AI分析</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6591300" cy="1857375"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="3114675"/>
+          <a:ext cx="6591300" cy="1857375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F9FAFB"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:srgbClr val="E5E7EB"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" i="1">
+              <a:solidFill>
+                <a:srgbClr val="9CA3AF"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic"/>
+              <a:cs typeface="Yu Gothic"/>
+            </a:rPr>
+            <a:t>※ 画面で AI 分析を生成するとここに表示されます</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2634,7 +3210,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -2876,17 +3452,19 @@
       <c r="A24" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="1:4" ht="22" customHeight="1">
       <c r="A25" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="22">
         <v>980</v>
       </c>
     </row>
@@ -2894,28 +3472,14 @@
       <c r="A26" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="25">
         <v>265</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="26" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-    </row>
-    <row r="31" spans="1:4" ht="54" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
@@ -2932,8 +3496,9 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -2945,7 +3510,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3001,27 +3566,27 @@
     <row r="3" spans="1:18" ht="6" customHeight="1"/>
     <row r="4" spans="1:18" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="F4" s="20" t="s">
         <v>83</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="22" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="22">
         <v>11850</v>
@@ -3033,7 +3598,7 @@
         <v>27254</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F5" s="22">
         <v>29</v>
@@ -3041,7 +3606,7 @@
     </row>
     <row r="6" spans="1:18" ht="22" customHeight="1">
       <c r="A6" s="24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B6" s="25">
         <v>11500</v>
@@ -3053,7 +3618,7 @@
         <v>26449</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F6" s="25">
         <v>28</v>
@@ -3061,7 +3626,7 @@
     </row>
     <row r="7" spans="1:18" ht="22" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" s="22">
         <v>11150</v>
@@ -3073,7 +3638,7 @@
         <v>25644</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7" s="22">
         <v>27</v>
@@ -3081,7 +3646,7 @@
     </row>
     <row r="8" spans="1:18" ht="22" customHeight="1">
       <c r="A8" s="24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8" s="25">
         <v>10800</v>
@@ -3093,7 +3658,7 @@
         <v>24839</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F8" s="25">
         <v>26</v>
@@ -3101,7 +3666,7 @@
     </row>
     <row r="9" spans="1:18" ht="22" customHeight="1">
       <c r="A9" s="21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" s="22">
         <v>10450</v>
@@ -3113,7 +3678,7 @@
         <v>24034</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F9" s="22">
         <v>25</v>
@@ -3121,7 +3686,7 @@
     </row>
     <row r="10" spans="1:18" ht="22" customHeight="1">
       <c r="A10" s="24" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B10" s="25">
         <v>10100</v>
@@ -3133,7 +3698,7 @@
         <v>23230</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F10" s="25">
         <v>24</v>
@@ -3141,7 +3706,7 @@
     </row>
     <row r="11" spans="1:18" ht="22" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B11" s="22">
         <v>9750</v>
@@ -3153,7 +3718,7 @@
         <v>22425</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F11" s="22">
         <v>23</v>
@@ -3161,7 +3726,7 @@
     </row>
     <row r="12" spans="1:18" ht="22" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B12" s="25">
         <v>9400</v>
@@ -3173,7 +3738,7 @@
         <v>21620</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F12" s="25">
         <v>22</v>
@@ -3181,7 +3746,7 @@
     </row>
     <row r="13" spans="1:18" ht="22" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13" s="22">
         <v>9050</v>
@@ -3193,7 +3758,7 @@
         <v>20815</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F13" s="22">
         <v>21</v>
@@ -3201,7 +3766,7 @@
     </row>
     <row r="14" spans="1:18" ht="22" customHeight="1">
       <c r="A14" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B14" s="25">
         <v>8700</v>
@@ -3213,7 +3778,7 @@
         <v>20010</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F14" s="25">
         <v>20</v>
@@ -3221,7 +3786,7 @@
     </row>
     <row r="15" spans="1:18" ht="22" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B15" s="22">
         <v>8350</v>
@@ -3233,7 +3798,7 @@
         <v>19205</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F15" s="22">
         <v>19</v>
@@ -3241,7 +3806,7 @@
     </row>
     <row r="16" spans="1:18" ht="22" customHeight="1">
       <c r="A16" s="24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B16" s="25">
         <v>8000</v>
@@ -3253,58 +3818,36 @@
         <v>18400</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F16" s="25">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="24" customHeight="1">
-      <c r="A17" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="31">
+      <c r="A17" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="29">
         <v>119100</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="29">
         <v>92898</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="29">
         <v>273925</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="31">
+      <c r="E17" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="29">
         <v>282</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="26" customHeight="1">
-      <c r="A20" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-    </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -3365,24 +3908,24 @@
     <row r="3" spans="1:15" ht="6" customHeight="1"/>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="33" customHeight="1">
+    </row>
+    <row r="5" spans="1:15" ht="22" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B5" s="22">
         <v>12500</v>
@@ -3394,12 +3937,12 @@
         <v>145</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="22" customHeight="1">
       <c r="A6" s="24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B6" s="25">
         <v>7200</v>
@@ -3411,12 +3954,12 @@
         <v>88</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="22" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B7" s="22">
         <v>3100</v>
@@ -3428,12 +3971,12 @@
         <v>31</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="33" customHeight="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="22" customHeight="1">
       <c r="A8" s="24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B8" s="25">
         <v>1800</v>
@@ -3445,24 +3988,24 @@
         <v>12</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="24" customHeight="1">
-      <c r="A9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="31">
+      <c r="A9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="29">
         <v>24600</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="29">
         <v>19000</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="29">
         <v>276</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>112</v>
+      <c r="E9" s="30" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3505,93 +4048,93 @@
     <row r="3" spans="1:3" ht="6" customHeight="1"/>
     <row r="4" spans="1:3" ht="24" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3" ht="24" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B6" s="22">
         <v>51200</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22" customHeight="1">
       <c r="A7" s="24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" s="25">
         <v>41600</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="24" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1">
       <c r="A11" s="21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B11" s="22">
         <v>60500</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22" customHeight="1">
       <c r="A12" s="24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B12" s="25">
         <v>27800</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1">
       <c r="A13" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B13" s="22">
         <v>4500</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3605,6 +4148,7 @@
   <headerFooter>
     <oddFooter>&amp;C© グローレポータ  Produced by GrowGroup Co.,Ltd.</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3635,7 +4179,7 @@
     <row r="3" spans="1:4" ht="6" customHeight="1"/>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>76</v>
@@ -3644,12 +4188,12 @@
         <v>77</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B5" s="22">
         <v>75</v>
@@ -3663,7 +4207,7 @@
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
       <c r="A6" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B6" s="25">
         <v>82</v>
@@ -3677,7 +4221,7 @@
     </row>
     <row r="7" spans="1:4" ht="22" customHeight="1">
       <c r="A7" s="21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B7" s="22">
         <v>90</v>
@@ -3691,7 +4235,7 @@
     </row>
     <row r="8" spans="1:4" ht="22" customHeight="1">
       <c r="A8" s="24" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B8" s="25">
         <v>110</v>
@@ -3704,16 +4248,16 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="31">
+      <c r="A9" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="29">
         <v>357</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="29">
         <v>95</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="29">
         <v>452</v>
       </c>
     </row>
@@ -3726,6 +4270,7 @@
   <headerFooter>
     <oddFooter>&amp;C© グローレポータ  Produced by GrowGroup Co.,Ltd.</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3738,14 +4283,15 @@
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="50.7109375" customWidth="1"/>
-    <col min="5" max="5" width="60.7109375" customWidth="1"/>
-    <col min="6" max="7" width="40.7109375" customWidth="1"/>
+    <col min="5" max="5" width="40.7109375" customWidth="1"/>
+    <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" customWidth="1"/>
     <col min="8" max="8" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -3757,7 +4303,7 @@
     </row>
     <row r="2" spans="1:8" ht="16" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -3770,28 +4316,28 @@
     <row r="3" spans="1:8" ht="6" customHeight="1"/>
     <row r="4" spans="1:8" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="F4" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="G4" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="H4" s="20" t="s">
         <v>138</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22" customHeight="1">
@@ -3799,25 +4345,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="F5" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="G5" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="H5" s="21" t="s">
         <v>145</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22" customHeight="1">
@@ -3825,25 +4371,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="F6" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="G6" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>154</v>
-      </c>
       <c r="H6" s="24" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
